--- a/forms/trg/Formulir_TRG_ohcirg.xlsx
+++ b/forms/trg/Formulir_TRG_ohcirg.xlsx
@@ -916,7 +916,11 @@
           <t>Prof. Fuad Husain Akbar., drg., MARS, Ph.D., FISQua</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
@@ -1279,7 +1283,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="12" t="n"/>
@@ -1316,7 +1320,7 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Lecturer</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="12" t="n"/>
